--- a/aq_files/0647.xlsx
+++ b/aq_files/0647.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="List_Methods" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,468 +413,483 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Question</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Details</t>
+          <t>Options</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Difficulty</t>
+          <t>Explanation</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>What is the first step in creating an Airflow workflow?</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>append() does:</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>A) add element B) remove C) sort D) none</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Import DAG and operators from airflow.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>What operator is used to run a Python function?</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pop() does:</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>A) remove last B) add C) sort D) none</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>PythonOperator executes Python callables.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>What symbol is used to set task dependencies?</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>sort() does:</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>A) sort list B) reverse C) add D) none</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>The bitshift operator defines task order.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MCQ</t>
+          <t>How do you set task A to run before task B?</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>len() gives:</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>A) length B) type C) value D) none</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>This creates a dependency where A runs before B.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>What is the purpose of the BashOperator?</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Implement stack using list.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>BashOperator runs bash commands or scripts.</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>What does the "task_id" parameter do?</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Implement queue using list.</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Each task must have a unique task_id within the DAG.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Scenario: A task needs to pass data to another task. What should be used?</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Reverse list using methods.</t>
+          <t>Scenario-based</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>A) Global variables,B) XComs,C) Environment variables,D) Database</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>XComs allow tasks to exchange messages.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>What is XCom?</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sort list without built-in.</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>XCom stands for cross-communication between tasks.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>What method pushes data to XCom?</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Remove duplicates using methods.</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>xcom_push sends data to the XCom backend.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>What method pulls data from XCom?</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Find kth largest element.</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>xcom_pull retrieves data from the XCom backend.</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>What is the default XCom size limit?</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rotate list using slicing.</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>The default limit is 48KB for performance reasons.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Which operator is used to wait for a file to appear?</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Find median of list.</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>FileSensor checks for file existence.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>What is a Sensor in Airflow?</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Merge lists and sort.</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>Sensors wait for a condition to be true.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>How do you set a task to retry on failure?</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Find min difference between elements.</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Set retries in default_args or task level.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>What is the purpose of the "depends_on_past" parameter?</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Check palindrome using list.</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>It prevents parallel execution of the same task.</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>What does the "wait_for_downstream" parameter do?</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Simulate push/pop operations.</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Easy</t>
+          <t>It ensures previous DAG run tasks complete.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Which decorator is used for taskflow API in Airflow 2.0?</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Find frequency using list.</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>@task decorator simplifies Python function tasks.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>What is the Taskflow API?</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Find sum of subarrays.</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Taskflow API reduces boilerplate code.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>Scenario: A DAG runs but tasks are stuck in "queued" state. What's likely wrong?</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Reverse list segments.</t>
+          <t>Scenario-based</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LeetCode-style problem</t>
+          <t>A) No workers running,B) Wrong schedule,C) XCom too large,D) Missing tags</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>Queued tasks indicate no workers are available.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Coding</t>
+          <t>What is the difference between BranchPythonOperator and PythonOperator?</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Find sliding window max.</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>LeetCode-style problem</t>
+          <t>One-word</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Hard</t>
+          <t>BranchPythonOperator chooses next task based on condition.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
